--- a/Result/profitability/8926.xlsx
+++ b/Result/profitability/8926.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>0.71</v>
+        <v>0.81375</v>
       </c>
       <c r="N2" t="n">
-        <v>10.75625</v>
+        <v>10.85125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.67375</v>
+        <v>0.75625</v>
       </c>
       <c r="N3" t="n">
-        <v>10.3075</v>
+        <v>10.17375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7575000000000001</v>
+        <v>0.845</v>
       </c>
       <c r="N4" t="n">
-        <v>9.678750000000001</v>
+        <v>9.512499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7312500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>8.543749999999999</v>
+        <v>7.0575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6162500000000001</v>
+        <v>0.74</v>
       </c>
       <c r="N6" t="n">
-        <v>6.16375</v>
+        <v>6.311249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6675</v>
+        <v>0.7424999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>6.38625</v>
+        <v>5.68375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.68</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.56375</v>
       </c>
       <c r="N8" t="n">
-        <v>11.55</v>
+        <v>11.6225</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8926</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20783</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18891</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1892</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1662</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>52</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K75" t="n">
+        <v>918</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.27375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4407582938388626</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.068075117370892</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.008403361344537785</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.89</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5664602191519772</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
